--- a/output/pdf_financials_xlsx/MUN.xlsx
+++ b/output/pdf_financials_xlsx/MUN.xlsx
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1.964876</v>
+        <v>-1.964876</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>1.593211</v>
+        <v>-1.593211</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>0.981572</v>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="O20" s="3" t="n">
-        <v>1.964876</v>
+        <v>-1.964876</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>1.593211</v>
+        <v>-1.593211</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>1.170135</v>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1.964876</v>
+        <v>-1.964876</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1.593211</v>
+        <v>-1.593211</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>1.170135</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-98.24379999999999</v>
+        <v>98.24379999999999</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-79.66055</v>
+        <v>79.66055</v>
       </c>
       <c r="Q26" s="1" t="inlineStr">
         <is>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1.964876</v>
+        <v>-1.964876</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1.593211</v>
+        <v>-1.593211</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>0.981572</v>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>2.015827</v>
+        <v>-1.913925</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.629973</v>
+        <v>-1.556449</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>1.064504</v>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>19.21030754748505</v>
@@ -6621,10 +6621,10 @@
         <v>4.456892</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>0.5297190000000001</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>0.067133</v>
       </c>
       <c r="G91" s="3" t="n">
         <v>0.098259</v>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="O99" s="3" t="n">
-        <v>1.964876</v>
+        <v>-1.964876</v>
       </c>
       <c r="P99" s="3" t="n">
         <v>-1.593211</v>
@@ -19422,7 +19422,11 @@
           <t>Foreign currency translation reserve (note 12(d))</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -20458,7 +20462,11 @@
           <t>Foreign currency translation reserve (note 12(e))</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -47917,10 +47925,10 @@
         </is>
       </c>
       <c r="R365" s="5" t="n">
-        <v>1.964876</v>
+        <v>-1.964876</v>
       </c>
       <c r="S365" s="5" t="n">
-        <v>1.593211</v>
+        <v>-1.593211</v>
       </c>
       <c r="T365" t="inlineStr">
         <is>
@@ -48129,10 +48137,10 @@
         </is>
       </c>
       <c r="R367" s="5" t="n">
-        <v>1.909196</v>
+        <v>-1.909196</v>
       </c>
       <c r="S367" s="5" t="n">
-        <v>1.491998</v>
+        <v>-1.491998</v>
       </c>
       <c r="T367" t="inlineStr">
         <is>
